--- a/reports/二级子公司D_利润表_2026-10.xlsx
+++ b/reports/二级子公司D_利润表_2026-10.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>89333866</v>
+        <v>91916348</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>87336395</v>
+        <v>87978110</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>866757324</v>
+        <v>866633656</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>301034</v>
+        <v>304484</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2929194</v>
+        <v>2933446</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>259535</v>
+        <v>260604</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2511220</v>
+        <v>2514525</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>217583</v>
+        <v>216699</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2093731</v>
+        <v>2095121</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>194301</v>
+        <v>194541</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1883680</v>
+        <v>1884981</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>107577</v>
+        <v>107820</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1046089</v>
+        <v>1046733</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>86838</v>
+        <v>86096</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>837282</v>
+        <v>836970</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>88166998</v>
+        <v>90746104</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>86169527</v>
+        <v>86807866</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4855224</v>
+        <v>4843551</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>47079521</v>
+        <v>47035802</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>380733</v>
+        <v>377445</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>3663830</v>
+        <v>3658568</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>649166</v>
+        <v>648616</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6279828</v>
+        <v>6273459</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>77403150</v>
+        <v>78028088</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>770494908</v>
+        <v>770390881</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1299871</v>
+        <v>1303234</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>12557400</v>
+        <v>12558250</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>434951</v>
+        <v>435014</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4187486</v>
+        <v>4188109</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2155600</v>
+        <v>2175964</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>20927568</v>
+        <v>20948757</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>538433</v>
+        <v>543643</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5230613</v>
+        <v>5238398</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1956162</v>
+        <v>1954033</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>18840630</v>
+        <v>18858784</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>41309</v>
+        <v>41263</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>412117</v>
+        <v>412427</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1166858</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>11309271</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>776084</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7535997</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>58673411</v>
+        <v>62835745</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>52599880</v>
+        <v>52582121</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>51623453</v>
+        <v>51613204</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>502121790</v>
+        <v>501773287</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>976427</v>
+        <v>968917</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>9419056</v>
+        <v>9407124</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1941733</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18815935</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>622882</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>6022806</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>390263</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3765860</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>469274</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4521272</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>352402</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3392570</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>234998</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2262558</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>195680</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1885852</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>924486</v>
+        <v>922491</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8898422</v>
+        <v>8905431</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>700942</v>
+        <v>703812</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6801719</v>
+        <v>6808649</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>538210</v>
+        <v>540033</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5230538</v>
+        <v>5235475</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4128068</v>
+        <v>4094867</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>39773337</v>
+        <v>39770683</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>154994</v>
+        <v>161372</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1545466</v>
+        <v>1569118</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>327773</v>
+        <v>327629</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3295264</v>
+        <v>3292872</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>370306</v>
+        <v>327629</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3707159</v>
+        <v>3292872</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41447</v>
+        <v>41022</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>412125</v>
+        <v>411469</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>166486</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1666721</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>340753</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3293886</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>111538</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1112106</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83817</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>834530</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>139856</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1391575</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>489558</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4713845</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>74532</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>742558</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55799</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>556883</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92780</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>927874</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>64783</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>649219</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46170</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>463479</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36879</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>370587</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27643</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>277821</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>29493587</v>
+        <v>29093231</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>33886441</v>
+        <v>32267823</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>194295</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1881703</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46377</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>463175</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>72527</v>
+        <v>72314</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>721203</v>
+        <v>720861</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>29421060</v>
+        <v>29215212</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2559795</v>
+        <v>2590120</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>25741427</v>
+        <v>25771369</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>26861265</v>
+        <v>26625092</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>26861265</v>
+        <v>26625092</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>26861265</v>
+        <v>26625092</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>26861265</v>
+        <v>26625092</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>26861265</v>
+        <v>26625092</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
